--- a/phase1/mai.xlsx
+++ b/phase1/mai.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m41den/Downloads/pm/PmProject/phase1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F27EBD-9492-E44E-811A-E300C2A413AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7198B9D7-AFD0-4FEB-AD45-006C770BA126}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Концепции и критерии" sheetId="1" r:id="rId1"/>
@@ -31,8 +31,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -505,12 +505,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -523,9 +517,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -543,7 +543,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -1027,7 +1027,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -1035,14 +1035,14 @@
     <col min="4" max="29" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>28</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
     </row>
-    <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1064,7 +1064,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>29</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>39</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>41</v>
       </c>
@@ -1141,7 +1141,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>43</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>45</v>
       </c>
@@ -1163,7 +1163,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>47</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
@@ -1185,7 +1185,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>1</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>2</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>3</v>
       </c>
@@ -1218,24 +1218,24 @@
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B23" s="6"/>
       <c r="C23" s="7" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B24" s="8"/>
       <c r="C24" s="7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>55</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B27" s="3">
         <v>1</v>
       </c>
@@ -1251,7 +1251,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B28" s="3">
         <v>3</v>
       </c>
@@ -1259,7 +1259,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B29" s="3">
         <v>5</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B30" s="3">
         <v>7</v>
       </c>
@@ -1275,7 +1275,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B31" s="3">
         <v>9</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="s">
         <v>62</v>
       </c>
@@ -1291,7 +1291,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
         <v>64</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
         <v>66</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B36" s="3">
         <v>3</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B37" s="3">
         <v>4</v>
       </c>
@@ -1323,7 +1323,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B38" s="3">
         <v>5</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B39" s="3">
         <v>6</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B40" s="3">
         <v>7</v>
       </c>
@@ -1347,8 +1347,8 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="31" t="s">
+    <row r="42" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="29" t="s">
         <v>68</v>
       </c>
       <c r="B42" s="28"/>
@@ -1366,13 +1366,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="29" width="12.5" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="29" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>69</v>
       </c>
@@ -1386,8 +1392,8 @@
       <c r="I1" s="28"/>
       <c r="J1" s="28"/>
     </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
         <v>70</v>
       </c>
       <c r="B2" s="28"/>
@@ -1400,21 +1406,21 @@
       <c r="I2" s="28"/>
       <c r="J2" s="28"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="32" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-    </row>
-    <row r="5" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+    </row>
+    <row r="5" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>37</v>
       </c>
@@ -1446,7 +1452,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>2</v>
       </c>
@@ -1482,7 +1488,7 @@
         <v>5.1947194401900045</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>3</v>
       </c>
@@ -1520,7 +1526,7 @@
         <v>5.58555951193184</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>4</v>
       </c>
@@ -1560,7 +1566,7 @@
         <v>5.0966151123212526</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>5</v>
       </c>
@@ -1599,7 +1605,7 @@
         <v>5.1947194401900036</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>6</v>
       </c>
@@ -1639,7 +1645,7 @@
         <v>5.4191981139283891</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>76</v>
       </c>
@@ -1648,7 +1654,7 @@
         <v>5.2981623237122975</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>77</v>
       </c>
@@ -1657,7 +1663,7 @@
         <v>7.4540580928074363E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>78</v>
       </c>
@@ -1665,27 +1671,27 @@
         <f>B12/'Концепции и критерии'!$C$38</f>
         <v>6.6554090114352107E-2</v>
       </c>
-      <c r="C13" s="34" t="str">
+      <c r="C13" s="32" t="str">
         <f>IF(B13&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D13" s="34"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="D13" s="32"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-    </row>
-    <row r="16" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+    </row>
+    <row r="16" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>37</v>
       </c>
@@ -1717,7 +1723,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>2</v>
       </c>
@@ -1753,7 +1759,7 @@
         <v>5.090080715597896</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>3</v>
       </c>
@@ -1790,7 +1796,7 @@
         <v>5.2131295115849303</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>4</v>
       </c>
@@ -1830,7 +1836,7 @@
         <v>5.1762372429565158</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>5</v>
       </c>
@@ -1869,7 +1875,7 @@
         <v>5.1597413673542212</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>6</v>
       </c>
@@ -1909,7 +1915,7 @@
         <v>5.0442257830492023</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>76</v>
       </c>
@@ -1918,7 +1924,7 @@
         <v>5.1366829241085536</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>77</v>
       </c>
@@ -1927,7 +1933,7 @@
         <v>3.4170731027138412E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>78</v>
       </c>
@@ -1935,27 +1941,27 @@
         <f>B23/'Концепции и критерии'!$C$38</f>
         <v>3.0509581274230722E-2</v>
       </c>
-      <c r="C24" s="34" t="str">
+      <c r="C24" s="32" t="str">
         <f>IF(B24&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D24" s="34"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="32" t="s">
+      <c r="D24" s="32"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="33"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-    </row>
-    <row r="27" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+    </row>
+    <row r="27" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>37</v>
       </c>
@@ -1987,7 +1993,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>2</v>
       </c>
@@ -2023,7 +2029,7 @@
         <v>5.0594978149165604</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>3</v>
       </c>
@@ -2061,7 +2067,7 @@
         <v>5.1330962028616547</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>4</v>
       </c>
@@ -2101,7 +2107,7 @@
         <v>5.0583429037912344</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>5</v>
       </c>
@@ -2140,7 +2146,7 @@
         <v>5.1134070910478115</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>6</v>
       </c>
@@ -2180,7 +2186,7 @@
         <v>5.0258286009725861</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
         <v>76</v>
       </c>
@@ -2189,7 +2195,7 @@
         <v>5.0780345227179691</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>77</v>
       </c>
@@ -2198,7 +2204,7 @@
         <v>1.9508630679492267E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>78</v>
       </c>
@@ -2206,27 +2212,27 @@
         <f>B34/'Концепции и критерии'!$C$38</f>
         <v>1.7418420249546665E-2</v>
       </c>
-      <c r="C35" s="34" t="str">
+      <c r="C35" s="32" t="str">
         <f>IF(B35&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D35" s="34"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37" s="32" t="s">
+      <c r="D35" s="32"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="B37" s="33"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
-    </row>
-    <row r="38" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+    </row>
+    <row r="38" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>37</v>
       </c>
@@ -2258,7 +2264,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>2</v>
       </c>
@@ -2299,7 +2305,7 @@
         <v>5.0343971567031485</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>3</v>
       </c>
@@ -2340,7 +2346,7 @@
         <v>5.0718314375534836</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>4</v>
       </c>
@@ -2381,7 +2387,7 @@
         <v>5.0652760344587158</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>5</v>
       </c>
@@ -2422,7 +2428,7 @@
         <v>5.0244514752630982</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>6</v>
       </c>
@@ -2463,7 +2469,7 @@
         <v>5.0404078920075799</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
         <v>76</v>
       </c>
@@ -2472,7 +2478,7 @@
         <v>5.0472727991972048</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>77</v>
       </c>
@@ -2481,7 +2487,7 @@
         <v>1.181819979930121E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
         <v>78</v>
       </c>
@@ -2489,11 +2495,11 @@
         <f>B45/'Концепции и критерии'!$C$38</f>
         <v>1.0551964106518937E-2</v>
       </c>
-      <c r="C46" s="34" t="str">
+      <c r="C46" s="32" t="str">
         <f>IF(B46&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D46" s="34"/>
+      <c r="D46" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2515,13 +2521,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="29" width="12.5" customWidth="1"/>
+    <col min="2" max="29" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>82</v>
       </c>
@@ -2535,8 +2541,8 @@
       <c r="I1" s="28"/>
       <c r="J1" s="28"/>
     </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
         <v>70</v>
       </c>
       <c r="B2" s="28"/>
@@ -2549,21 +2555,21 @@
       <c r="I2" s="28"/>
       <c r="J2" s="28"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="32" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-    </row>
-    <row r="5" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+    </row>
+    <row r="5" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>83</v>
       </c>
@@ -2595,7 +2601,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>9</v>
       </c>
@@ -2631,7 +2637,7 @@
         <v>5.1361870798887974</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>10</v>
       </c>
@@ -2670,7 +2676,7 @@
         <v>5.030137824251141</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>11</v>
       </c>
@@ -2709,7 +2715,7 @@
         <v>5.0436693333896878</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>12</v>
       </c>
@@ -2749,7 +2755,7 @@
         <v>5.030137824251141</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
@@ -2789,7 +2795,7 @@
         <v>5.1174855277363536</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>76</v>
       </c>
@@ -2798,7 +2804,7 @@
         <v>5.0715235179034241</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>77</v>
       </c>
@@ -2807,7 +2813,7 @@
         <v>1.7880879475856037E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>78</v>
       </c>
@@ -2815,27 +2821,27 @@
         <f>B12/'Концепции и критерии'!$C$38</f>
         <v>1.5965070960585748E-2</v>
       </c>
-      <c r="C13" s="34" t="str">
+      <c r="C13" s="32" t="str">
         <f>IF(B13&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D13" s="34"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="D13" s="32"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-    </row>
-    <row r="16" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+    </row>
+    <row r="16" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>83</v>
       </c>
@@ -2867,7 +2873,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>9</v>
       </c>
@@ -2903,7 +2909,7 @@
         <v>5.1075864454640714</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>10</v>
       </c>
@@ -2942,7 +2948,7 @@
         <v>5.082842875430309</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>11</v>
       </c>
@@ -2980,7 +2986,7 @@
         <v>5.0359116879549646</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>12</v>
       </c>
@@ -3020,7 +3026,7 @@
         <v>5.0137611814737273</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>13</v>
       </c>
@@ -3060,7 +3066,7 @@
         <v>5.0359116879549646</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>76</v>
       </c>
@@ -3069,7 +3075,7 @@
         <v>5.0552027756556068</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>77</v>
       </c>
@@ -3078,7 +3084,7 @@
         <v>1.3800693913901707E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>78</v>
       </c>
@@ -3086,27 +3092,27 @@
         <f>B23/'Концепции и критерии'!$C$38</f>
         <v>1.2322048137412236E-2</v>
       </c>
-      <c r="C24" s="34" t="str">
+      <c r="C24" s="32" t="str">
         <f>IF(B24&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D24" s="34"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="32" t="s">
+      <c r="D24" s="32"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="33"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-    </row>
-    <row r="27" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+    </row>
+    <row r="27" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>83</v>
       </c>
@@ -3138,7 +3144,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>9</v>
       </c>
@@ -3174,7 +3180,7 @@
         <v>5.0729861623457797</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>10</v>
       </c>
@@ -3213,7 +3219,7 @@
         <v>5.0539325106372175</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>11</v>
       </c>
@@ -3251,7 +3257,7 @@
         <v>5.1423159126515854</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>12</v>
       </c>
@@ -3291,7 +3297,7 @@
         <v>5.0252657163593621</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>13</v>
       </c>
@@ -3331,7 +3337,7 @@
         <v>5.1255725710506548</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
         <v>76</v>
       </c>
@@ -3340,7 +3346,7 @@
         <v>5.0840145746089194</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>77</v>
       </c>
@@ -3349,7 +3355,7 @@
         <v>2.1003643652229842E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>78</v>
       </c>
@@ -3357,27 +3363,27 @@
         <f>B34/'Концепции и критерии'!$C$38</f>
         <v>1.8753253260919499E-2</v>
       </c>
-      <c r="C35" s="34" t="str">
+      <c r="C35" s="32" t="str">
         <f>IF(B35&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D35" s="34"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37" s="32" t="s">
+      <c r="D35" s="32"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="B37" s="33"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
-    </row>
-    <row r="38" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+    </row>
+    <row r="38" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>83</v>
       </c>
@@ -3409,7 +3415,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>9</v>
       </c>
@@ -3450,7 +3456,7 @@
         <v>5.0758971391692516</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>10</v>
       </c>
@@ -3491,7 +3497,7 @@
         <v>5.0482175818995465</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>11</v>
       </c>
@@ -3532,7 +3538,7 @@
         <v>5.0171768179942351</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>12</v>
       </c>
@@ -3573,7 +3579,7 @@
         <v>5.0164268841454369</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>13</v>
       </c>
@@ -3614,7 +3620,7 @@
         <v>5.0425927461468305</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
         <v>76</v>
       </c>
@@ -3623,7 +3629,7 @@
         <v>5.0400622338710601</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>77</v>
       </c>
@@ -3632,7 +3638,7 @@
         <v>1.0015558467765029E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
         <v>78</v>
       </c>
@@ -3640,11 +3646,11 @@
         <f>B45/'Концепции и критерии'!$C$38</f>
         <v>8.942462917647347E-3</v>
       </c>
-      <c r="C46" s="34" t="str">
+      <c r="C46" s="32" t="str">
         <f>IF(B46&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D46" s="34"/>
+      <c r="D46" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3666,13 +3672,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="29" width="12.5" customWidth="1"/>
+    <col min="2" max="29" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>84</v>
       </c>
@@ -3686,8 +3692,8 @@
       <c r="I1" s="28"/>
       <c r="J1" s="28"/>
     </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
         <v>70</v>
       </c>
       <c r="B2" s="28"/>
@@ -3700,21 +3706,21 @@
       <c r="I2" s="28"/>
       <c r="J2" s="28"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="32" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-    </row>
-    <row r="5" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+    </row>
+    <row r="5" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>85</v>
       </c>
@@ -3746,7 +3752,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>9</v>
       </c>
@@ -3782,7 +3788,7 @@
         <v>5.0910728398540561</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>10</v>
       </c>
@@ -3819,7 +3825,7 @@
         <v>5.0727739010480128</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>11</v>
       </c>
@@ -3857,7 +3863,7 @@
         <v>5.1149009432772159</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>12</v>
       </c>
@@ -3896,7 +3902,7 @@
         <v>5.0761385971464001</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
@@ -3936,7 +3942,7 @@
         <v>5.1142531675838372</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>76</v>
       </c>
@@ -3945,7 +3951,7 @@
         <v>5.0938278897819043</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>77</v>
       </c>
@@ -3954,7 +3960,7 @@
         <v>2.3456972445476065E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>78</v>
       </c>
@@ -3962,27 +3968,27 @@
         <f>B12/'Концепции и критерии'!$C$38</f>
         <v>2.0943725397746485E-2</v>
       </c>
-      <c r="C13" s="34" t="str">
+      <c r="C13" s="32" t="str">
         <f>IF(B13&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D13" s="34"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="D13" s="32"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-    </row>
-    <row r="16" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+    </row>
+    <row r="16" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>85</v>
       </c>
@@ -4014,7 +4020,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>9</v>
       </c>
@@ -4053,7 +4059,7 @@
         <v>5.0963826264364913</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>10</v>
       </c>
@@ -4090,7 +4096,7 @@
         <v>5.1319629929811077</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>11</v>
       </c>
@@ -4128,7 +4134,7 @@
         <v>5.0834760046257799</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>12</v>
       </c>
@@ -4167,7 +4173,7 @@
         <v>5.1119118116458626</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>13</v>
       </c>
@@ -4207,7 +4213,7 @@
         <v>5.063457737222854</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>76</v>
       </c>
@@ -4216,7 +4222,7 @@
         <v>5.0974382345824196</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>77</v>
       </c>
@@ -4225,7 +4231,7 @@
         <v>2.4359558645604906E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>78</v>
       </c>
@@ -4233,27 +4239,27 @@
         <f>B23/'Концепции и критерии'!$C$38</f>
         <v>2.1749605933575809E-2</v>
       </c>
-      <c r="C24" s="34" t="str">
+      <c r="C24" s="32" t="str">
         <f>IF(B24&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D24" s="34"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="32" t="s">
+      <c r="D24" s="32"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="33"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-    </row>
-    <row r="27" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+    </row>
+    <row r="27" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>85</v>
       </c>
@@ -4285,7 +4291,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>9</v>
       </c>
@@ -4321,7 +4327,7 @@
         <v>5.1273682563987704</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>10</v>
       </c>
@@ -4358,7 +4364,7 @@
         <v>5.019248918293159</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>11</v>
       </c>
@@ -4396,7 +4402,7 @@
         <v>5.019248918293159</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>12</v>
       </c>
@@ -4435,7 +4441,7 @@
         <v>5.1058490203775522</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>13</v>
       </c>
@@ -4475,7 +4481,7 @@
         <v>5.0192489182931599</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
         <v>76</v>
       </c>
@@ -4484,7 +4490,7 @@
         <v>5.0581928063311592</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>77</v>
       </c>
@@ -4493,7 +4499,7 @@
         <v>1.4548201582789799E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>78</v>
       </c>
@@ -4501,27 +4507,27 @@
         <f>B34/'Концепции и критерии'!$C$38</f>
         <v>1.2989465698919463E-2</v>
       </c>
-      <c r="C35" s="34" t="str">
+      <c r="C35" s="32" t="str">
         <f>IF(B35&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D35" s="34"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37" s="32" t="s">
+      <c r="D35" s="32"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="B37" s="33"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
-    </row>
-    <row r="38" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+    </row>
+    <row r="38" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>85</v>
       </c>
@@ -4553,7 +4559,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>9</v>
       </c>
@@ -4594,7 +4600,7 @@
         <v>5.0165270983560797</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>10</v>
       </c>
@@ -4635,7 +4641,7 @@
         <v>5.0092712957233649</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>11</v>
       </c>
@@ -4676,7 +4682,7 @@
         <v>5.016716037723139</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>12</v>
       </c>
@@ -4717,7 +4723,7 @@
         <v>5.0294116079841471</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>13</v>
       </c>
@@ -4758,7 +4764,7 @@
         <v>5.021505636245827</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
         <v>76</v>
       </c>
@@ -4767,7 +4773,7 @@
         <v>5.0186863352065121</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>77</v>
       </c>
@@ -4776,7 +4782,7 @@
         <v>4.6715838016280209E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
         <v>78</v>
       </c>
@@ -4784,11 +4790,11 @@
         <f>B45/'Концепции и критерии'!$C$38</f>
         <v>4.1710569657393039E-3</v>
       </c>
-      <c r="C46" s="34" t="str">
+      <c r="C46" s="32" t="str">
         <f>IF(B46&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D46" s="34"/>
+      <c r="D46" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -4810,13 +4816,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="29" width="12.5" customWidth="1"/>
+    <col min="2" max="29" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>86</v>
       </c>
@@ -4830,8 +4836,8 @@
       <c r="I1" s="28"/>
       <c r="J1" s="28"/>
     </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
         <v>70</v>
       </c>
       <c r="B2" s="28"/>
@@ -4844,21 +4850,21 @@
       <c r="I2" s="28"/>
       <c r="J2" s="28"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="32" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-    </row>
-    <row r="5" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+    </row>
+    <row r="5" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>87</v>
       </c>
@@ -4890,7 +4896,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>9</v>
       </c>
@@ -4928,7 +4934,7 @@
         <v>5.0533001044538848</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>10</v>
       </c>
@@ -4965,7 +4971,7 @@
         <v>5.1658727254414858</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>11</v>
       </c>
@@ -5004,7 +5010,7 @@
         <v>5.1727428471019872</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>12</v>
       </c>
@@ -5043,7 +5049,7 @@
         <v>5.0136409250066807</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
@@ -5083,7 +5089,7 @@
         <v>5.0533001044538848</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>76</v>
       </c>
@@ -5092,7 +5098,7 @@
         <v>5.0917713412915848</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>77</v>
       </c>
@@ -5101,7 +5107,7 @@
         <v>2.2942835322896205E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>78</v>
       </c>
@@ -5109,27 +5115,27 @@
         <f>B12/'Концепции и критерии'!$C$38</f>
         <v>2.0484674395443037E-2</v>
       </c>
-      <c r="C13" s="34" t="str">
+      <c r="C13" s="32" t="str">
         <f>IF(B13&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D13" s="34"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="D13" s="32"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-    </row>
-    <row r="16" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+    </row>
+    <row r="16" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>87</v>
       </c>
@@ -5161,7 +5167,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>9</v>
       </c>
@@ -5199,7 +5205,7 @@
         <v>5.0153329563001128</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>10</v>
       </c>
@@ -5236,7 +5242,7 @@
         <v>5.1585475264552354</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>11</v>
       </c>
@@ -5275,7 +5281,7 @@
         <v>5.0153329563001128</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>12</v>
       </c>
@@ -5314,7 +5320,7 @@
         <v>5.1413423332943129</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>13</v>
       </c>
@@ -5354,7 +5360,7 @@
         <v>5.0538651146503293</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>76</v>
       </c>
@@ -5363,7 +5369,7 @@
         <v>5.0768841774000206</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>77</v>
       </c>
@@ -5372,7 +5378,7 @@
         <v>1.9221044350005156E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>78</v>
       </c>
@@ -5380,27 +5386,27 @@
         <f>B23/'Концепции и критерии'!$C$38</f>
         <v>1.716164674107603E-2</v>
       </c>
-      <c r="C24" s="34" t="str">
+      <c r="C24" s="32" t="str">
         <f>IF(B24&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D24" s="34"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="32" t="s">
+      <c r="D24" s="32"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="33"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-    </row>
-    <row r="27" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+    </row>
+    <row r="27" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>87</v>
       </c>
@@ -5432,7 +5438,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>9</v>
       </c>
@@ -5468,7 +5474,7 @@
         <v>5.1450359455704691</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>10</v>
       </c>
@@ -5505,7 +5511,7 @@
         <v>5.129161676004685</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>11</v>
       </c>
@@ -5544,7 +5550,7 @@
         <v>5.0690910738848265</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>12</v>
       </c>
@@ -5583,7 +5589,7 @@
         <v>5.0401014513276126</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>13</v>
       </c>
@@ -5623,7 +5629,7 @@
         <v>5.0401014513276126</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
         <v>76</v>
       </c>
@@ -5632,7 +5638,7 @@
         <v>5.0846983196230413</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>77</v>
       </c>
@@ -5641,7 +5647,7 @@
         <v>2.1174579905760327E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>78</v>
       </c>
@@ -5649,27 +5655,27 @@
         <f>B34/'Концепции и критерии'!$C$38</f>
         <v>1.8905874915857431E-2</v>
       </c>
-      <c r="C35" s="34" t="str">
+      <c r="C35" s="32" t="str">
         <f>IF(B35&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D35" s="34"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37" s="32" t="s">
+      <c r="D35" s="32"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="B37" s="33"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
-    </row>
-    <row r="38" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+    </row>
+    <row r="38" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>87</v>
       </c>
@@ -5701,7 +5707,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>9</v>
       </c>
@@ -5742,7 +5748,7 @@
         <v>5.0427164886147953</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>10</v>
       </c>
@@ -5783,7 +5789,7 @@
         <v>5.0668468523422758</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>11</v>
       </c>
@@ -5824,7 +5830,7 @@
         <v>5.0324099998841554</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>12</v>
       </c>
@@ -5865,7 +5871,7 @@
         <v>5.0143491256838333</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>13</v>
       </c>
@@ -5906,7 +5912,7 @@
         <v>5.0192524933368885</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
         <v>76</v>
       </c>
@@ -5915,7 +5921,7 @@
         <v>5.0351149919723897</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>77</v>
       </c>
@@ -5924,7 +5930,7 @@
         <v>8.7787479930974133E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
         <v>78</v>
       </c>
@@ -5932,11 +5938,11 @@
         <f>B45/'Концепции и критерии'!$C$38</f>
         <v>7.8381678509798318E-3</v>
       </c>
-      <c r="C46" s="34" t="str">
+      <c r="C46" s="32" t="str">
         <f>IF(B46&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D46" s="34"/>
+      <c r="D46" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -5958,13 +5964,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="29" width="12.5" customWidth="1"/>
+    <col min="2" max="29" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>88</v>
       </c>
@@ -5978,8 +5984,8 @@
       <c r="I1" s="28"/>
       <c r="J1" s="28"/>
     </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
         <v>70</v>
       </c>
       <c r="B2" s="28"/>
@@ -5992,21 +5998,21 @@
       <c r="I2" s="28"/>
       <c r="J2" s="28"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="32" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-    </row>
-    <row r="5" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+    </row>
+    <row r="5" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>89</v>
       </c>
@@ -6038,7 +6044,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>9</v>
       </c>
@@ -6074,7 +6080,7 @@
         <v>5.0205412166312389</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>10</v>
       </c>
@@ -6113,7 +6119,7 @@
         <v>5.0644075479668986</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>11</v>
       </c>
@@ -6152,7 +6158,7 @@
         <v>5.0709028519776318</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>12</v>
       </c>
@@ -6192,7 +6198,7 @@
         <v>5.0206984849645684</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
@@ -6232,7 +6238,7 @@
         <v>5.0578535168381835</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>76</v>
       </c>
@@ -6241,7 +6247,7 @@
         <v>5.0468807236757041</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>77</v>
       </c>
@@ -6250,7 +6256,7 @@
         <v>1.1720180918926015E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>78</v>
       </c>
@@ -6258,27 +6264,27 @@
         <f>B12/'Концепции и критерии'!$C$38</f>
         <v>1.0464447249041085E-2</v>
       </c>
-      <c r="C13" s="34" t="str">
+      <c r="C13" s="32" t="str">
         <f>IF(B13&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D13" s="34"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="D13" s="32"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-    </row>
-    <row r="16" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+    </row>
+    <row r="16" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>89</v>
       </c>
@@ -6310,7 +6316,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>9</v>
       </c>
@@ -6346,7 +6352,7 @@
         <v>5.1298767308171689</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>10</v>
       </c>
@@ -6385,7 +6391,7 @@
         <v>5.0226744664132754</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>11</v>
       </c>
@@ -6423,7 +6429,7 @@
         <v>5.1091589722165995</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>12</v>
       </c>
@@ -6463,7 +6469,7 @@
         <v>5.025704263966678</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>13</v>
       </c>
@@ -6503,7 +6509,7 @@
         <v>5.0226744664132736</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>76</v>
       </c>
@@ -6512,7 +6518,7 @@
         <v>5.0620177799653998</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>77</v>
       </c>
@@ -6521,7 +6527,7 @@
         <v>1.5504444991349953E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>78</v>
       </c>
@@ -6529,27 +6535,27 @@
         <f>B23/'Концепции и критерии'!$C$38</f>
         <v>1.3843254456562457E-2</v>
       </c>
-      <c r="C24" s="34" t="str">
+      <c r="C24" s="32" t="str">
         <f>IF(B24&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D24" s="34"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="32" t="s">
+      <c r="D24" s="32"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="33"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-    </row>
-    <row r="27" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+    </row>
+    <row r="27" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>89</v>
       </c>
@@ -6581,7 +6587,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>9</v>
       </c>
@@ -6617,7 +6623,7 @@
         <v>5.0462846817141411</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>10</v>
       </c>
@@ -6656,7 +6662,7 @@
         <v>5.0038662917444974</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>11</v>
       </c>
@@ -6694,7 +6700,7 @@
         <v>5.1057184634058359</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>12</v>
       </c>
@@ -6734,7 +6740,7 @@
         <v>5.0415735446503902</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>13</v>
       </c>
@@ -6774,7 +6780,7 @@
         <v>5.0959231754633958</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
         <v>76</v>
       </c>
@@ -6783,7 +6789,7 @@
         <v>5.0586732313956517</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>77</v>
       </c>
@@ -6792,7 +6798,7 @@
         <v>1.4668307848912931E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>78</v>
       </c>
@@ -6800,27 +6806,27 @@
         <f>B34/'Концепции и критерии'!$C$38</f>
         <v>1.3096703436529402E-2</v>
       </c>
-      <c r="C35" s="34" t="str">
+      <c r="C35" s="32" t="str">
         <f>IF(B35&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D35" s="34"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37" s="32" t="s">
+      <c r="D35" s="32"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="B37" s="33"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
-    </row>
-    <row r="38" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+    </row>
+    <row r="38" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>89</v>
       </c>
@@ -6852,7 +6858,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>9</v>
       </c>
@@ -6893,7 +6899,7 @@
         <v>5.0442340878575678</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>10</v>
       </c>
@@ -6934,7 +6940,7 @@
         <v>5.0140973252402876</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>11</v>
       </c>
@@ -6975,7 +6981,7 @@
         <v>5.0402030360169725</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>12</v>
       </c>
@@ -7016,7 +7022,7 @@
         <v>5.0008846076526652</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>13</v>
       </c>
@@ -7057,7 +7063,7 @@
         <v>5.0145047030715926</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
         <v>76</v>
       </c>
@@ -7066,7 +7072,7 @@
         <v>5.0227847519678175</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>77</v>
       </c>
@@ -7075,7 +7081,7 @@
         <v>5.6961879919543712E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
         <v>78</v>
       </c>
@@ -7083,11 +7089,11 @@
         <f>B45/'Концепции и критерии'!$C$38</f>
         <v>5.0858821356735452E-3</v>
       </c>
-      <c r="C46" s="34" t="str">
+      <c r="C46" s="32" t="str">
         <f>IF(B46&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D46" s="34"/>
+      <c r="D46" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -7109,13 +7115,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:J46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="29" width="12.5" customWidth="1"/>
+    <col min="2" max="29" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>90</v>
       </c>
@@ -7129,8 +7135,8 @@
       <c r="I1" s="28"/>
       <c r="J1" s="28"/>
     </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
         <v>70</v>
       </c>
       <c r="B2" s="28"/>
@@ -7143,21 +7149,21 @@
       <c r="I2" s="28"/>
       <c r="J2" s="28"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="32" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-    </row>
-    <row r="5" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+    </row>
+    <row r="5" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>91</v>
       </c>
@@ -7189,7 +7195,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>9</v>
       </c>
@@ -7225,7 +7231,7 @@
         <v>5.1950575432555226</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>10</v>
       </c>
@@ -7263,7 +7269,7 @@
         <v>5.2429432360877888</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>11</v>
       </c>
@@ -7301,7 +7307,7 @@
         <v>5.039526795401601</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>12</v>
       </c>
@@ -7341,7 +7347,7 @@
         <v>5.038836835895216</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
@@ -7381,7 +7387,7 @@
         <v>5.3187616564344804</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>76</v>
       </c>
@@ -7390,7 +7396,7 @@
         <v>5.1670252134149219</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>77</v>
       </c>
@@ -7399,7 +7405,7 @@
         <v>4.1756303353730484E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>78</v>
       </c>
@@ -7407,27 +7413,27 @@
         <f>B12/'Концепции и критерии'!$C$38</f>
         <v>3.7282413708687928E-2</v>
       </c>
-      <c r="C13" s="34" t="str">
+      <c r="C13" s="32" t="str">
         <f>IF(B13&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D13" s="34"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="D13" s="32"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-    </row>
-    <row r="16" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+    </row>
+    <row r="16" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>91</v>
       </c>
@@ -7459,7 +7465,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>9</v>
       </c>
@@ -7495,7 +7501,7 @@
         <v>5.1679507186327962</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>10</v>
       </c>
@@ -7534,7 +7540,7 @@
         <v>5.0441386327912587</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>11</v>
       </c>
@@ -7572,7 +7578,7 @@
         <v>5.0164891099542031</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>12</v>
       </c>
@@ -7612,7 +7618,7 @@
         <v>5.0791040556407729</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>13</v>
       </c>
@@ -7652,7 +7658,7 @@
         <v>5.1263029701952361</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>76</v>
       </c>
@@ -7661,7 +7667,7 @@
         <v>5.0867970974428536</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>77</v>
       </c>
@@ -7670,7 +7676,7 @@
         <v>2.1699274360713394E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>78</v>
       </c>
@@ -7678,27 +7684,27 @@
         <f>B23/'Концепции и критерии'!$C$38</f>
         <v>1.9374352107779814E-2</v>
       </c>
-      <c r="C24" s="34" t="str">
+      <c r="C24" s="32" t="str">
         <f>IF(B24&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D24" s="34"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="32" t="s">
+      <c r="D24" s="32"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="33"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-    </row>
-    <row r="27" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+    </row>
+    <row r="27" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>91</v>
       </c>
@@ -7730,7 +7736,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>9</v>
       </c>
@@ -7766,7 +7772,7 @@
         <v>5.0141159728058176</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>10</v>
       </c>
@@ -7805,7 +7811,7 @@
         <v>5.0714843592905217</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>11</v>
       </c>
@@ -7843,7 +7849,7 @@
         <v>5.0706717711283451</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>12</v>
       </c>
@@ -7882,7 +7888,7 @@
         <v>5.1146923092870296</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>13</v>
       </c>
@@ -7922,7 +7928,7 @@
         <v>5.0882536706336072</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
         <v>76</v>
       </c>
@@ -7931,7 +7937,7 @@
         <v>5.0718436166290646</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>77</v>
       </c>
@@ -7940,7 +7946,7 @@
         <v>1.7960904157266144E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>78</v>
       </c>
@@ -7948,27 +7954,27 @@
         <f>B34/'Концепции и критерии'!$C$38</f>
         <v>1.6036521568987626E-2</v>
       </c>
-      <c r="C35" s="34" t="str">
+      <c r="C35" s="32" t="str">
         <f>IF(B35&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D35" s="34"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37" s="32" t="s">
+      <c r="D35" s="32"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="B37" s="33"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
-    </row>
-    <row r="38" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+    </row>
+    <row r="38" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>91</v>
       </c>
@@ -8000,7 +8006,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>9</v>
       </c>
@@ -8041,7 +8047,7 @@
         <v>5.0062160750162557</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>10</v>
       </c>
@@ -8082,7 +8088,7 @@
         <v>5.0301152025575178</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>11</v>
       </c>
@@ -8123,7 +8129,7 @@
         <v>5.0204733212478585</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>12</v>
       </c>
@@ -8164,7 +8170,7 @@
         <v>5.0121370325838868</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>13</v>
       </c>
@@ -8205,7 +8211,7 @@
         <v>5.0137955321617982</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
         <v>76</v>
       </c>
@@ -8214,7 +8220,7 @@
         <v>5.0165474327134634</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>77</v>
       </c>
@@ -8223,7 +8229,7 @@
         <v>4.1368581783658431E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
         <v>78</v>
       </c>
@@ -8231,11 +8237,11 @@
         <f>B45/'Концепции и критерии'!$C$38</f>
         <v>3.6936233735409309E-3</v>
       </c>
-      <c r="C46" s="34" t="str">
+      <c r="C46" s="32" t="str">
         <f>IF(B46&lt;=0.1,"согласована (ОС ≤ 10%)","требует пересмотра")</f>
         <v>согласована (ОС ≤ 10%)</v>
       </c>
-      <c r="D46" s="34"/>
+      <c r="D46" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -8257,13 +8263,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:H19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="29" width="14" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="29" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -8275,7 +8285,7 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="3" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -8301,7 +8311,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>9</v>
       </c>
@@ -8334,7 +8344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>10</v>
       </c>
@@ -8367,7 +8377,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>11</v>
       </c>
@@ -8400,7 +8410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>12</v>
       </c>
@@ -8433,7 +8443,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>13</v>
       </c>
@@ -8466,7 +8476,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>14</v>
       </c>
@@ -8496,22 +8506,22 @@
       </c>
       <c r="H9" s="23"/>
     </row>
-    <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="29" t="str">
+      <c r="B10" s="33" t="str">
         <f>INDEX($A$4:$A$8,MATCH(MAX($G$4:$G$8),$G$4:$G$8,0))</f>
         <v>Сплит</v>
       </c>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-    </row>
-    <row r="12" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+    </row>
+    <row r="12" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
         <v>16</v>
       </c>
@@ -8523,7 +8533,7 @@
       <c r="G12" s="28"/>
       <c r="H12" s="28"/>
     </row>
-    <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
@@ -8540,7 +8550,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>22</v>
       </c>
@@ -8561,7 +8571,7 @@
         <v>1.0551964106518937E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>23</v>
       </c>
@@ -8582,7 +8592,7 @@
         <v>8.942462917647347E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>24</v>
       </c>
@@ -8603,7 +8613,7 @@
         <v>4.1710569657393039E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -8624,7 +8634,7 @@
         <v>7.8381678509798318E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -8645,7 +8655,7 @@
         <v>5.0858821356735452E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>27</v>
       </c>
